--- a/СДАЧА/ЛР2-3/SW_объем_рынка_Similarweb_NotaCode.xlsx
+++ b/СДАЧА/ЛР2-3/SW_объем_рынка_Similarweb_NotaCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ИИТ\ЭлектронныйБизнес\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ИИТ\ЭлектронныйБизнес\СДАЧА\ЛР2-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7441449-14AF-4C08-A853-3A2CDCDEB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09BCE15-F9A8-4140-AF96-C1CD62896DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="11_Вариант_М2" sheetId="52" r:id="rId1"/>
@@ -37,9 +37,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1380,7 +1377,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0\ \₽"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1407,10 +1404,12 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1420,8 +1419,13 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1458,6 +1462,12 @@
         <fgColor rgb="FFF8FBFD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1472,7 +1482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1533,6 +1543,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1603,7 +1615,7 @@
             <c:numRef>
               <c:f>'07_Дашборд'!$B$11:$B$13</c:f>
               <c:numCache>
-                <c:formatCode>#\ ##0\ \₽</c:formatCode>
+                <c:formatCode>#,##0\ \₽</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>7689.7210919760009</c:v>
@@ -1651,7 +1663,7 @@
             <c:numRef>
               <c:f>'07_Дашборд'!$C$11:$C$13</c:f>
               <c:numCache>
-                <c:formatCode>#\ ##0\ \₽</c:formatCode>
+                <c:formatCode>#,##0\ \₽</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>38.448605459880007</c:v>
@@ -1728,7 +1740,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#\ ##0\ \₽" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0\ \₽" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2332,10 +2344,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73ED5EEF-DE88-46F6-9D76-97C5CED46B8B}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="60.5625" customWidth="1"/>
-    <col min="2" max="7" width="22.5625" customWidth="1"/>
+    <col min="1" max="1" width="60.625" customWidth="1"/>
+    <col min="2" max="7" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2615,7 +2627,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="26" customWidth="1"/>
@@ -2669,7 +2681,7 @@
       <c r="I3" s="27"/>
       <c r="J3" s="27"/>
     </row>
-    <row r="4" spans="1:26" ht="27.75">
+    <row r="4" spans="1:26" ht="30">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -2823,7 +2835,7 @@
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
     </row>
-    <row r="11" spans="1:26" ht="27.75">
+    <row r="11" spans="1:26" ht="30">
       <c r="A11" s="1" t="s">
         <v>207</v>
       </c>
@@ -2923,7 +2935,7 @@
       <c r="I17" s="27"/>
       <c r="J17" s="27"/>
     </row>
-    <row r="18" spans="1:10" ht="108">
+    <row r="18" spans="1:10" ht="114">
       <c r="A18" s="2" t="s">
         <v>230</v>
       </c>
@@ -2989,7 +3001,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" ht="27">
+    <row r="21" spans="1:10" ht="28.5">
       <c r="A21" s="2" t="s">
         <v>236</v>
       </c>
@@ -3016,7 +3028,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="94.5">
+    <row r="22" spans="1:10" ht="99.75">
       <c r="A22" s="2" t="s">
         <v>239</v>
       </c>
@@ -3051,7 +3063,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -3109,7 +3121,7 @@
       <c r="K3" s="27"/>
       <c r="L3" s="27"/>
     </row>
-    <row r="4" spans="1:26" ht="81">
+    <row r="4" spans="1:26" ht="85.5">
       <c r="A4" s="14" t="s">
         <v>242</v>
       </c>
@@ -3146,7 +3158,7 @@
         <v>25189.670000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="27.75">
+    <row r="5" spans="1:26" ht="30">
       <c r="A5" s="14" t="s">
         <v>247</v>
       </c>
@@ -3183,7 +3195,7 @@
         <v>Organic search</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="27.75">
+    <row r="6" spans="1:26" ht="30">
       <c r="A6" s="14" t="s">
         <v>252</v>
       </c>
@@ -3213,7 +3225,7 @@
         <v>2033.8139558000003</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="94.5">
+    <row r="7" spans="1:26" ht="99.75">
       <c r="A7" s="14" t="s">
         <v>256</v>
       </c>
@@ -3232,7 +3244,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="27.75">
+    <row r="10" spans="1:26" ht="30">
       <c r="A10" s="1" t="s">
         <v>207</v>
       </c>
@@ -3282,7 +3294,7 @@
         <v>4893.5262018300018</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="13.9">
+    <row r="16" spans="1:26" ht="15">
       <c r="A16" s="1" t="s">
         <v>154</v>
       </c>
@@ -3384,7 +3396,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -3574,7 +3586,7 @@
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
     </row>
-    <row r="13" spans="1:26" ht="13.9">
+    <row r="13" spans="1:26" ht="15">
       <c r="A13" s="1" t="s">
         <v>297</v>
       </c>
@@ -3775,10 +3787,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E167DE7C-5FA1-468F-BF79-286D4C5B0382}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="60.5625" customWidth="1"/>
-    <col min="2" max="7" width="22.5625" customWidth="1"/>
+    <col min="1" max="1" width="60.625" customWidth="1"/>
+    <col min="2" max="7" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3934,10 +3946,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD4A868-3920-4730-8E20-BAE88A902F48}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="60.5625" customWidth="1"/>
-    <col min="2" max="7" width="22.5625" customWidth="1"/>
+    <col min="1" max="1" width="60.625" customWidth="1"/>
+    <col min="2" max="7" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4301,7 +4313,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z18"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -4368,7 +4380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="27">
+    <row r="4" spans="1:26" ht="42.75">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -4394,7 +4406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="27">
+    <row r="5" spans="1:26" ht="28.5">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -4420,7 +4432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="27">
+    <row r="6" spans="1:26" ht="28.5">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -4446,7 +4458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="27">
+    <row r="7" spans="1:26" ht="28.5">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -4472,7 +4484,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="40.5">
+    <row r="8" spans="1:26" ht="42.75">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -4498,7 +4510,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="27">
+    <row r="9" spans="1:26" ht="42.75">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -4524,7 +4536,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="27">
+    <row r="10" spans="1:26" ht="28.5">
       <c r="A10" s="2" t="s">
         <v>56</v>
       </c>
@@ -4550,7 +4562,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="27">
+    <row r="11" spans="1:26" ht="28.5">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -4588,7 +4600,7 @@
       <c r="G13" s="27"/>
       <c r="H13" s="27"/>
     </row>
-    <row r="14" spans="1:26" ht="27">
+    <row r="14" spans="1:26" ht="28.5">
       <c r="A14" s="2" t="s">
         <v>73</v>
       </c>
@@ -4606,7 +4618,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="40.5">
+    <row r="15" spans="1:26" ht="42.75">
       <c r="A15" s="2" t="s">
         <v>77</v>
       </c>
@@ -4624,7 +4636,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="27">
+    <row r="16" spans="1:26" ht="28.5">
       <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
@@ -4660,7 +4672,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" ht="27">
+    <row r="18" spans="1:8" ht="28.5">
       <c r="A18" s="2" t="s">
         <v>89</v>
       </c>
@@ -4693,7 +4705,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z20"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -4972,7 +4984,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -5660,7 +5672,7 @@
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
     </row>
-    <row r="25" spans="1:19" ht="13.9">
+    <row r="25" spans="1:19" ht="15">
       <c r="A25" s="6" t="s">
         <v>152</v>
       </c>
@@ -5694,27 +5706,27 @@
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="9">
-        <f>IFERROR(SUMPRODUCT($G$4:$G$23,M4:M23)/SUMIF(M4:M23,"&gt;0",$G$4:$G$23),0)</f>
+        <f t="shared" ref="M25:R25" si="3">IFERROR(SUMPRODUCT($G$4:$G$23,M4:M23)/SUMIF(M4:M23,"&gt;0",$G$4:$G$23),0)</f>
         <v>0</v>
       </c>
       <c r="N25" s="9">
-        <f>IFERROR(SUMPRODUCT($G$4:$G$23,N4:N23)/SUMIF(N4:N23,"&gt;0",$G$4:$G$23),0)</f>
+        <f t="shared" si="3"/>
         <v>0.48469999999999996</v>
       </c>
       <c r="O25" s="9">
-        <f>IFERROR(SUMPRODUCT($G$4:$G$23,O4:O23)/SUMIF(O4:O23,"&gt;0",$G$4:$G$23),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P25" s="9">
-        <f>IFERROR(SUMPRODUCT($G$4:$G$23,P4:P23)/SUMIF(P4:P23,"&gt;0",$G$4:$G$23),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q25" s="9">
-        <f>IFERROR(SUMPRODUCT($G$4:$G$23,Q4:Q23)/SUMIF(Q4:Q23,"&gt;0",$G$4:$G$23),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R25" s="9">
-        <f>IFERROR(SUMPRODUCT($G$4:$G$23,R4:R23)/SUMIF(R4:R23,"&gt;0",$G$4:$G$23),0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S25" s="6"/>
@@ -5808,7 +5820,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
@@ -6105,7 +6117,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6384,7 +6396,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -6457,9 +6469,12 @@
       <c r="J3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="29" t="s">
         <v>351</v>
       </c>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
